--- a/table/resources/sample/DailyRewards.xlsx
+++ b/table/resources/sample/DailyRewards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="DailyRewards" sheetId="2" r:id="rId1"/>
@@ -55,12 +55,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+condition表中条件</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
   <si>
     <t>序列ID</t>
   </si>
@@ -74,12 +96,18 @@
     <t>签到奖励</t>
   </si>
   <si>
+    <t>领取奖励条件</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -92,40 +120,31 @@
     <t>getItem</t>
   </si>
   <si>
-    <t>1990000_350000</t>
-  </si>
-  <si>
-    <t>1022501_2</t>
-  </si>
-  <si>
-    <t>1990000_700000</t>
-  </si>
-  <si>
-    <t>1980000_50</t>
-  </si>
-  <si>
-    <t>1990000_1050000</t>
-  </si>
-  <si>
-    <t>1022502_2</t>
-  </si>
-  <si>
-    <t>1980000_100|1022503_2|1022501_2</t>
-  </si>
-  <si>
-    <t>1022501_4|1990000_1050000</t>
-  </si>
-  <si>
-    <t>1022502_2|1990000_1239000</t>
-  </si>
-  <si>
-    <t>1980000_100|1990000_1925000</t>
-  </si>
-  <si>
-    <t>1022503_2|1990000_2989000</t>
-  </si>
-  <si>
-    <t>1980000_300|1990000_4025000</t>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>1990000_2000</t>
+  </si>
+  <si>
+    <t>todayDeposit(1,0)</t>
+  </si>
+  <si>
+    <t>1990000_3000</t>
+  </si>
+  <si>
+    <t>1990000_5000</t>
+  </si>
+  <si>
+    <t>1990000_8000</t>
+  </si>
+  <si>
+    <t>1990000_10000</t>
+  </si>
+  <si>
+    <t>1990000_12000</t>
+  </si>
+  <si>
+    <t>1990000_20000</t>
   </si>
 </sst>
 </file>
@@ -1122,15 +1141,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="46" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="21.125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1143,42 +1163,51 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1189,10 +1218,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1203,10 +1235,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1217,10 +1252,13 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1231,10 +1269,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1245,10 +1286,13 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1259,10 +1303,13 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>19</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1273,10 +1320,13 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>20</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1">
         <v>101</v>
       </c>
@@ -1286,11 +1336,14 @@
       <c r="C12" s="5">
         <v>7</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="D12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1">
         <v>102</v>
       </c>
@@ -1300,11 +1353,14 @@
       <c r="C13" s="5">
         <v>14</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="D13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="1">
         <v>103</v>
       </c>
@@ -1314,11 +1370,14 @@
       <c r="C14" s="5">
         <v>19</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="D14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1">
         <v>104</v>
       </c>
@@ -1329,10 +1388,13 @@
         <v>24</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>18</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="1">
         <v>105</v>
       </c>
@@ -1340,10 +1402,13 @@
         <v>2</v>
       </c>
       <c r="C16" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/table/resources/sample/DailyRewards.xlsx
+++ b/table/resources/sample/DailyRewards.xlsx
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>序列ID</t>
   </si>
@@ -123,28 +123,37 @@
     <t>condition</t>
   </si>
   <si>
-    <t>1990000_2000</t>
+    <t>1990000_6000</t>
   </si>
   <si>
     <t>todayDeposit(1,0)</t>
   </si>
   <si>
-    <t>1990000_3000</t>
-  </si>
-  <si>
-    <t>1990000_5000</t>
-  </si>
-  <si>
-    <t>1990000_8000</t>
-  </si>
-  <si>
-    <t>1990000_10000</t>
-  </si>
-  <si>
     <t>1990000_12000</t>
   </si>
   <si>
-    <t>1990000_20000</t>
+    <t>1990000_18000</t>
+  </si>
+  <si>
+    <t>1990000_24000</t>
+  </si>
+  <si>
+    <t>1990000_36000</t>
+  </si>
+  <si>
+    <t>1990000_30000</t>
+  </si>
+  <si>
+    <t>1990000_45000</t>
+  </si>
+  <si>
+    <t>1990000_60000</t>
+  </si>
+  <si>
+    <t>1990000_75000</t>
+  </si>
+  <si>
+    <t>1990000_90000</t>
   </si>
 </sst>
 </file>
@@ -1235,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>14</v>
@@ -1252,7 +1261,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>14</v>
@@ -1269,7 +1278,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>14</v>
@@ -1286,7 +1295,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -1303,7 +1312,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>14</v>
@@ -1320,7 +1329,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>14</v>
@@ -1334,10 +1343,10 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>14</v>
@@ -1351,10 +1360,10 @@
         <v>2</v>
       </c>
       <c r="C13" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>14</v>
@@ -1368,10 +1377,10 @@
         <v>2</v>
       </c>
       <c r="C14" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>14</v>
@@ -1388,7 +1397,7 @@
         <v>24</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>14</v>
@@ -1405,7 +1414,7 @@
         <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>14</v>

--- a/table/resources/sample/DailyRewards.xlsx
+++ b/table/resources/sample/DailyRewards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="DailyRewards" sheetId="2" r:id="rId1"/>
@@ -141,19 +141,19 @@
     <t>1990000_36000</t>
   </si>
   <si>
-    <t>1990000_30000</t>
-  </si>
-  <si>
-    <t>1990000_45000</t>
-  </si>
-  <si>
     <t>1990000_60000</t>
   </si>
   <si>
-    <t>1990000_75000</t>
-  </si>
-  <si>
-    <t>1990000_90000</t>
+    <t>1990000_120000</t>
+  </si>
+  <si>
+    <t>1990000_180000</t>
+  </si>
+  <si>
+    <t>1990000_300000</t>
+  </si>
+  <si>
+    <t>1990000_540000</t>
   </si>
 </sst>
 </file>
@@ -331,12 +331,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/table/resources/sample/DailyRewards.xlsx
+++ b/table/resources/sample/DailyRewards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="DailyRewards" sheetId="2" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
   <si>
     <t>序列ID</t>
   </si>
@@ -123,37 +123,28 @@
     <t>condition</t>
   </si>
   <si>
-    <t>1990000_6000</t>
+    <t>1990000_2000</t>
   </si>
   <si>
     <t>todayDeposit(1,0)</t>
   </si>
   <si>
+    <t>1990000_3000</t>
+  </si>
+  <si>
+    <t>1990000_5000</t>
+  </si>
+  <si>
+    <t>1990000_8000</t>
+  </si>
+  <si>
+    <t>1990000_10000</t>
+  </si>
+  <si>
     <t>1990000_12000</t>
   </si>
   <si>
-    <t>1990000_18000</t>
-  </si>
-  <si>
-    <t>1990000_24000</t>
-  </si>
-  <si>
-    <t>1990000_36000</t>
-  </si>
-  <si>
-    <t>1990000_60000</t>
-  </si>
-  <si>
-    <t>1990000_120000</t>
-  </si>
-  <si>
-    <t>1990000_180000</t>
-  </si>
-  <si>
-    <t>1990000_300000</t>
-  </si>
-  <si>
-    <t>1990000_540000</t>
+    <t>1990000_20000</t>
   </si>
 </sst>
 </file>
@@ -331,12 +322,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1244,7 +1235,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>14</v>
@@ -1261,7 +1252,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>14</v>
@@ -1278,7 +1269,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>14</v>
@@ -1295,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -1312,7 +1303,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>14</v>
@@ -1329,7 +1320,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>14</v>
@@ -1343,10 +1334,10 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>14</v>
@@ -1360,10 +1351,10 @@
         <v>2</v>
       </c>
       <c r="C13" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>14</v>
@@ -1377,10 +1368,10 @@
         <v>2</v>
       </c>
       <c r="C14" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>14</v>
@@ -1397,7 +1388,7 @@
         <v>24</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>14</v>
@@ -1414,7 +1405,7 @@
         <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>14</v>

--- a/table/resources/sample/DailyRewards.xlsx
+++ b/table/resources/sample/DailyRewards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="DailyRewards" sheetId="2" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
   <si>
     <t>序列ID</t>
   </si>
@@ -123,37 +123,34 @@
     <t>condition</t>
   </si>
   <si>
-    <t>1990000_6000</t>
+    <t>1990000_75000</t>
   </si>
   <si>
     <t>todayDeposit(1,0)</t>
   </si>
   <si>
-    <t>1990000_12000</t>
-  </si>
-  <si>
-    <t>1990000_18000</t>
-  </si>
-  <si>
-    <t>1990000_24000</t>
-  </si>
-  <si>
-    <t>1990000_36000</t>
-  </si>
-  <si>
-    <t>1990000_60000</t>
-  </si>
-  <si>
-    <t>1990000_120000</t>
-  </si>
-  <si>
-    <t>1990000_180000</t>
+    <t>1990000_150000</t>
+  </si>
+  <si>
+    <t>1990000_225000</t>
   </si>
   <si>
     <t>1990000_300000</t>
   </si>
   <si>
-    <t>1990000_540000</t>
+    <t>1990000_450000</t>
+  </si>
+  <si>
+    <t>1990000_600000</t>
+  </si>
+  <si>
+    <t>1990000_900000</t>
+  </si>
+  <si>
+    <t>1990000_1500000</t>
+  </si>
+  <si>
+    <t>1990000_2700000</t>
   </si>
 </sst>
 </file>
@@ -331,12 +328,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1346,7 +1343,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>14</v>
@@ -1363,7 +1360,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>14</v>
@@ -1380,7 +1377,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>14</v>
@@ -1397,7 +1394,7 @@
         <v>24</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>14</v>
@@ -1414,7 +1411,7 @@
         <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>14</v>

--- a/table/resources/sample/DailyRewards.xlsx
+++ b/table/resources/sample/DailyRewards.xlsx
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
   <si>
     <t>序列ID</t>
   </si>
@@ -123,28 +123,34 @@
     <t>condition</t>
   </si>
   <si>
-    <t>1990000_2000</t>
+    <t>1990000_75000</t>
   </si>
   <si>
     <t>todayDeposit(1,0)</t>
   </si>
   <si>
-    <t>1990000_3000</t>
-  </si>
-  <si>
-    <t>1990000_5000</t>
-  </si>
-  <si>
-    <t>1990000_8000</t>
-  </si>
-  <si>
-    <t>1990000_10000</t>
-  </si>
-  <si>
-    <t>1990000_12000</t>
-  </si>
-  <si>
-    <t>1990000_20000</t>
+    <t>1990000_150000</t>
+  </si>
+  <si>
+    <t>1990000_225000</t>
+  </si>
+  <si>
+    <t>1990000_300000</t>
+  </si>
+  <si>
+    <t>1990000_450000</t>
+  </si>
+  <si>
+    <t>1990000_600000</t>
+  </si>
+  <si>
+    <t>1990000_900000</t>
+  </si>
+  <si>
+    <t>1990000_1500000</t>
+  </si>
+  <si>
+    <t>1990000_2700000</t>
   </si>
 </sst>
 </file>
@@ -1235,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>14</v>
@@ -1252,7 +1258,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>14</v>
@@ -1269,7 +1275,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>14</v>
@@ -1286,7 +1292,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -1303,7 +1309,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>14</v>
@@ -1320,7 +1326,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>14</v>
@@ -1334,10 +1340,10 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>14</v>
@@ -1351,10 +1357,10 @@
         <v>2</v>
       </c>
       <c r="C13" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>14</v>
@@ -1368,10 +1374,10 @@
         <v>2</v>
       </c>
       <c r="C14" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>14</v>
@@ -1388,7 +1394,7 @@
         <v>24</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>14</v>
@@ -1405,7 +1411,7 @@
         <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>14</v>
